--- a/ZonasEscolares/excels/PUNO-SAN_ROMAN-SAN_MIGUEL.xlsx
+++ b/ZonasEscolares/excels/PUNO-SAN_ROMAN-SAN_MIGUEL.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -503,12 +503,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -555,12 +555,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -763,12 +763,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAN_MIGUEL</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PUNO-SAN_ROMAN-SAN_MIGUEL.xlsx
+++ b/ZonasEscolares/excels/PUNO-SAN_ROMAN-SAN_MIGUEL.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>70582</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-15.460243</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-70.11622300000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>206</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-15.460243</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-70.116223</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>70606</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-15.47999</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-70.12448999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>595</v>
-      </c>
-      <c r="J3" t="n">
-        <v>31</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-15.47999</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-70.12449</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>1364 / 70613</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-15.47479</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-70.13269</v>
-      </c>
-      <c r="I4" t="n">
-        <v>505</v>
-      </c>
-      <c r="J4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-15.47479</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-70.13269</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>70618</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-15.47496</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-70.12067999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>624</v>
-      </c>
-      <c r="J5" t="n">
-        <v>29</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-15.47496</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-70.12068</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>70671 / SAN ISIDRO DE CCACCACHI</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-15.45378</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-70.09966</v>
-      </c>
-      <c r="I6" t="n">
-        <v>618</v>
-      </c>
-      <c r="J6" t="n">
-        <v>30</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-15.45378</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-70.09966</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>PERU BIRF</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-15.47937</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-70.13538</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1396</v>
-      </c>
-      <c r="J7" t="n">
-        <v>105</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-15.47937</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-70.13538</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-15.474425</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-70.117339</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1265</v>
-      </c>
-      <c r="J8" t="n">
-        <v>70</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-15.474425</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-70.117339</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>REAL CONVICTORIO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-15.481831</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-70.122095</v>
-      </c>
-      <c r="I9" t="n">
-        <v>271</v>
-      </c>
-      <c r="J9" t="n">
-        <v>18</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-15.481831</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-70.122095</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>GALILEO GALILEI</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-15.472805</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-70.12106</v>
-      </c>
-      <c r="I10" t="n">
-        <v>216</v>
-      </c>
-      <c r="J10" t="n">
-        <v>17</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-15.472805</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-70.12106</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-15.4744</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-70.13290000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>396</v>
-      </c>
-      <c r="J11" t="n">
-        <v>32</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-15.4744</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-70.1329</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>70605 DOMINGO SAVIO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-15.47724</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-70.12701</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1089</v>
-      </c>
-      <c r="J12" t="n">
-        <v>43</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-15.47724</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-70.12701</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1089</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>PEDRO VILCAPAZA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-15.47774</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-70.12737</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1685</v>
-      </c>
-      <c r="J13" t="n">
-        <v>81</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-15.47774</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-70.12737</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1685</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>961</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-15.47191</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-70.12248</v>
-      </c>
-      <c r="I14" t="n">
-        <v>33</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-15.47191</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-70.12248</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>DANIEL GOLEMAN</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-15.475556</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-70.134649</v>
-      </c>
-      <c r="I15" t="n">
-        <v>250</v>
-      </c>
-      <c r="J15" t="n">
-        <v>18</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-15.475556</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-70.134649</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>LA RECOLETA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-15.4677</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-70.11922</v>
-      </c>
-      <c r="I16" t="n">
-        <v>205</v>
-      </c>
-      <c r="J16" t="n">
-        <v>13</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-15.4677</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-70.11922</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>70660</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-15.47328</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-70.12815999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>216</v>
-      </c>
-      <c r="J17" t="n">
-        <v>14</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-15.47328</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-70.12816</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>70709</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-15.46492</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-70.1345</v>
-      </c>
-      <c r="I18" t="n">
-        <v>447</v>
-      </c>
-      <c r="J18" t="n">
-        <v>16</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-15.46492</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-70.1345</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>VIVA ESPERANZA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-15.478935</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-70.127999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>258</v>
-      </c>
-      <c r="J19" t="n">
-        <v>21</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-15.478935</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-70.127999</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>NUEVO PERU</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-15.46544</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-70.13135</v>
-      </c>
-      <c r="I20" t="n">
-        <v>758</v>
-      </c>
-      <c r="J20" t="n">
-        <v>32</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-15.46544</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-70.13135</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>ALBERT EINSTEIN</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-15.469693</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-70.11879500000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>578</v>
-      </c>
-      <c r="J21" t="n">
-        <v>29</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-15.469693</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-70.118795</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>NIKOLAS TESLA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-15.47293</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-70.12296000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>7</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-15.47293</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-70.12296</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/PUNO-SAN_ROMAN-SAN_MIGUEL.xlsx
+++ b/ZonasEscolares/excels/PUNO-SAN_ROMAN-SAN_MIGUEL.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>463608</t>
+          <t>852231</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70582</t>
+          <t>NIKOLAS TESLA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-15.460243</t>
+          <t>-15.47293</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-70.116223</t>
+          <t>-70.12296</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>463665</t>
+          <t>463929</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70606</t>
+          <t>PERU BIRF</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-15.47999</t>
+          <t>-15.47937</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-70.12449</t>
+          <t>-70.13538</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>105</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>463712</t>
+          <t>781173</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1364 / 70613</t>
+          <t>LA RECOLETA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-15.47479</t>
+          <t>-15.4677</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-70.13269</t>
+          <t>-70.11922</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>463769</t>
+          <t>794415</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70618</t>
+          <t>70660</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-15.47496</t>
+          <t>-15.47328</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-70.12068</t>
+          <t>-70.12816</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>463830</t>
+          <t>463608</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70671 / SAN ISIDRO DE CCACCACHI</t>
+          <t>70582</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-15.45378</t>
+          <t>-15.460243</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-70.09966</t>
+          <t>-70.116223</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>463929</t>
+          <t>794444</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PERU BIRF</t>
+          <t>70709</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-15.47937</t>
+          <t>-15.46492</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-70.13538</t>
+          <t>-70.1345</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>447</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>464009</t>
+          <t>554585</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SIMON BOLIVAR</t>
+          <t>GALILEO GALILEI</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-15.474425</t>
+          <t>-15.472805</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-70.117339</t>
+          <t>-70.12106</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>554585</t>
+          <t>757516</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GALILEO GALILEI</t>
+          <t>DANIEL GOLEMAN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-15.472805</t>
+          <t>-15.475556</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-70.12106</t>
+          <t>-70.134649</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>557937</t>
+          <t>690234</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HORACIO ZEVALLOS GAMEZ</t>
+          <t>961</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-15.4744</t>
+          <t>-15.47191</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-70.1329</t>
+          <t>-70.12248</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>649621</t>
+          <t>794929</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70605 DOMINGO SAVIO</t>
+          <t>VIVA ESPERANZA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-15.47724</t>
+          <t>-15.478935</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-70.12701</t>
+          <t>-70.127999</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>258</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>649664</t>
+          <t>463712</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PEDRO VILCAPAZA</t>
+          <t>1364 / 70613</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-15.47774</t>
+          <t>-15.47479</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-70.12737</t>
+          <t>-70.13269</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>505</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>690234</t>
+          <t>463769</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>70618</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-15.47191</t>
+          <t>-15.47496</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-70.12248</t>
+          <t>-70.12068</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>624</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>757516</t>
+          <t>835067</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DANIEL GOLEMAN</t>
+          <t>ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-15.475556</t>
+          <t>-15.469693</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-70.134649</t>
+          <t>-70.118795</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>578</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>781173</t>
+          <t>463830</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LA RECOLETA</t>
+          <t>70671 / SAN ISIDRO DE CCACCACHI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-15.4677</t>
+          <t>-15.45378</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-70.11922</t>
+          <t>-70.09966</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>618</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>794415</t>
+          <t>463665</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70660</t>
+          <t>70606</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-15.47328</t>
+          <t>-15.47999</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-70.12816</t>
+          <t>-70.12449</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>595</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>794444</t>
+          <t>557937</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70709</t>
+          <t>HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-15.46492</t>
+          <t>-15.4744</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-70.1345</t>
+          <t>-70.1329</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>396</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>794929</t>
+          <t>803735</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VIVA ESPERANZA</t>
+          <t>NUEVO PERU</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-15.478935</t>
+          <t>-15.46544</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-70.127999</t>
+          <t>-70.13135</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>758</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>803735</t>
+          <t>649621</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NUEVO PERU</t>
+          <t>70605 DOMINGO SAVIO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-15.46544</t>
+          <t>-15.47724</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-70.13135</t>
+          <t>-70.12701</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>835067</t>
+          <t>464009</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN</t>
+          <t>SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-15.469693</t>
+          <t>-15.474425</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-70.118795</t>
+          <t>-70.117339</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,37 +1741,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>852231</t>
+          <t>649664</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NIKOLAS TESLA</t>
+          <t>PEDRO VILCAPAZA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-15.47293</t>
+          <t>-15.47774</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-70.12296</t>
+          <t>-70.12737</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">

--- a/ZonasEscolares/excels/PUNO-SAN_ROMAN-SAN_MIGUEL.xlsx
+++ b/ZonasEscolares/excels/PUNO-SAN_ROMAN-SAN_MIGUEL.xlsx
@@ -511,22 +511,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>-15.47293</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>-70.12296</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>463929</t>
+          <t>835067</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PERU BIRF</t>
+          <t>ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-15.47937</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-70.13538</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>-15.469693</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>-70.118795</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>781173</t>
+          <t>803735</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LA RECOLETA</t>
+          <t>NUEVO PERU</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-15.4677</t>
+          <t>758</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-70.11922</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-15.46544</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-70.13135</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>794415</t>
+          <t>794929</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70660</t>
+          <t>VIVA ESPERANZA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-15.47328</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-70.12816</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>-15.478935</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-70.127999</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>463608</t>
+          <t>794444</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70582</t>
+          <t>70709</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-15.460243</t>
+          <t>447</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-70.116223</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-15.46492</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-70.1345</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>794444</t>
+          <t>794415</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70709</t>
+          <t>70660</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-15.46492</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-70.1345</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>-15.47328</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-70.12816</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>554585</t>
+          <t>781173</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GALILEO GALILEI</t>
+          <t>LA RECOLETA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-15.472805</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-70.12106</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>-15.4677</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-70.11922</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>464448</t>
+          <t>757516</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>REAL CONVICTORIO</t>
+          <t>DANIEL GOLEMAN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-15.481831</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-70.122095</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-15.475556</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-70.134649</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>757516</t>
+          <t>690234</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DANIEL GOLEMAN</t>
+          <t>961</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-15.475556</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-70.134649</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>-15.47191</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-70.12248</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>690234</t>
+          <t>649664</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>PEDRO VILCAPAZA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-15.47191</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-70.12248</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-15.47774</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-70.12737</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>794929</t>
+          <t>649621</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VIVA ESPERANZA</t>
+          <t>70605 DOMINGO SAVIO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-15.478935</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-70.127999</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>-15.47724</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.12701</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>463712</t>
+          <t>557937</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1364 / 70613</t>
+          <t>HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-15.47479</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-70.13269</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>-15.4744</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-70.1329</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>463769</t>
+          <t>554585</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70618</t>
+          <t>GALILEO GALILEI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-15.47496</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-70.12068</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>-15.472805</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-70.12106</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>835067</t>
+          <t>464448</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN</t>
+          <t>REAL CONVICTORIO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-15.469693</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-70.118795</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>-15.481831</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-70.122095</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>463830</t>
+          <t>464009</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70671 / SAN ISIDRO DE CCACCACHI</t>
+          <t>SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-15.45378</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-70.09966</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>-15.474425</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-70.117339</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>463665</t>
+          <t>463929</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70606</t>
+          <t>PERU BIRF</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-15.47999</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-70.12449</t>
+          <t>105</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>-15.47937</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-70.13538</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>557937</t>
+          <t>463830</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>HORACIO ZEVALLOS GAMEZ</t>
+          <t>70671 / SAN ISIDRO DE CCACCACHI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-15.4744</t>
+          <t>618</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-70.1329</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>-15.45378</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-70.09966</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>803735</t>
+          <t>463769</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NUEVO PERU</t>
+          <t>70618</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-15.46544</t>
+          <t>624</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-70.13135</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>-15.47496</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-70.12068</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>649621</t>
+          <t>463712</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70605 DOMINGO SAVIO</t>
+          <t>1364 / 70613</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-15.47724</t>
+          <t>505</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-70.12701</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>-15.47479</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-70.13269</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>464009</t>
+          <t>463665</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SIMON BOLIVAR</t>
+          <t>70606</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-15.474425</t>
+          <t>595</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-70.117339</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>-15.47999</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-70.12449</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>649664</t>
+          <t>463608</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PEDRO VILCAPAZA</t>
+          <t>70582</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-15.47774</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-70.12737</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>-15.460243</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>-70.116223</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">

--- a/ZonasEscolares/excels/PUNO-SAN_ROMAN-SAN_MIGUEL.xlsx
+++ b/ZonasEscolares/excels/PUNO-SAN_ROMAN-SAN_MIGUEL.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
